--- a/Result/profitability/4550.xlsx
+++ b/Result/profitability/4550.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM55"/>
+  <dimension ref="A1:AM56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7415,6 +7415,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>4550</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>147</v>
+      </c>
+      <c r="D56" t="n">
+        <v>115</v>
+      </c>
+      <c r="E56" t="n">
+        <v>32</v>
+      </c>
+      <c r="F56" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="G56" t="n">
+        <v>10</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>6.86%</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>2</v>
+      </c>
+      <c r="J56" t="n">
+        <v>12</v>
+      </c>
+      <c r="K56" t="n">
+        <v>10</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.6012500000000001</v>
+      </c>
+      <c r="N56" t="n">
+        <v>18.86125</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
+      </c>
+      <c r="V56" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W56" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="X56" t="n">
+        <v>-0.5806451612903225</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>-0.05096660808435849</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.363636363636364</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>6.330000000000002</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.4145383104125737</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK56" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
